--- a/Sajjad data/by_country_and_state/USA/NJ.xlsx
+++ b/Sajjad data/by_country_and_state/USA/NJ.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="575">
   <si>
     <t>Business Name</t>
   </si>
@@ -890,6 +890,852 @@
   </si>
   <si>
     <t>2026-10-25T23:10:24.253Z</t>
+  </si>
+  <si>
+    <t>Park Dental Center</t>
+  </si>
+  <si>
+    <t>(973) 881-8568</t>
+  </si>
+  <si>
+    <t>82 Park Ave, Paterson, NJ 07501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Park+Dental+Center/data=!4m7!3m6!1s0x89c2fc36e947cd91:0x25f04c4605823737!8m2!3d40.9152144!4d-74.163207!16s%2Fg%2F1tq6ff30!19sChIJkc1H6Tb8wokRNzeCBUZM8CU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:17.550Z</t>
+  </si>
+  <si>
+    <t>Hernandez Dental Office/.</t>
+  </si>
+  <si>
+    <t>(973) 247-9700</t>
+  </si>
+  <si>
+    <t>491 21st Ave Apt 1, Paterson, NJ 07513</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hernandez+Dental+Office%2F./data=!4m7!3m6!1s0x89c2fc23427929f3:0x240d45677ae63e43!8m2!3d40.9057945!4d-74.1523069!16s%2Fg%2F1tdq21ng!19sChIJ8yl5QiP8wokRQz7memdFDSQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:20.523Z</t>
+  </si>
+  <si>
+    <t>Dental PM</t>
+  </si>
+  <si>
+    <t>(973) 247-2580</t>
+  </si>
+  <si>
+    <t>301 Main St, Paterson, NJ 07505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+PM/data=!4m7!3m6!1s0x89c2fdcb32a2bc43:0x4f218c82ccf8316f!8m2!3d40.9150269!4d-74.1720514!16s%2Fg%2F11cmdmn222!19sChIJQ7yiMsv9wokRbzH4zIKMIU8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:23.075Z</t>
+  </si>
+  <si>
+    <t>Dental Care Center</t>
+  </si>
+  <si>
+    <t>(973) 595-8083</t>
+  </si>
+  <si>
+    <t>426 Union Ave, Paterson, NJ 07502</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Care+Center/data=!4m7!3m6!1s0x89c2fdc78f56650b:0x56a3b8de17a553d2!8m2!3d40.9213665!4d-74.1847692!16s%2Fg%2F1tklrh7y!19sChIJC2VWj8f9wokR0lOlF964o1Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:24.700Z</t>
+  </si>
+  <si>
+    <t>21st Avenue Dental</t>
+  </si>
+  <si>
+    <t>(973) 742-1991</t>
+  </si>
+  <si>
+    <t>318 21st Ave #102, Paterson, NJ 07501</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/21st+Avenue+Dental/data=!4m7!3m6!1s0x89c2fc2f945ec2d5:0x7f784f90fb502f9f!8m2!3d40.9070634!4d-74.1604342!16s%2Fg%2F11bvcvkyhz!19sChIJ1cJelC_8wokRny9Q-5BPeH8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:26.521Z</t>
+  </si>
+  <si>
+    <t>South Paterson Family Dentistry</t>
+  </si>
+  <si>
+    <t>(973) 881-7800</t>
+  </si>
+  <si>
+    <t>32 Hine St #106, Paterson, NJ 07503</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/South+Paterson+Family+Dentistry/data=!4m7!3m6!1s0x89c2fc2a36eb2eb9:0x330a79426dc478f1!8m2!3d40.901297!4d-74.1662855!16s%2Fg%2F1tfkm32v!19sChIJuS7rNir8wokR8XjEbUJ5CjM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:29.885Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentistry Paterson</t>
+  </si>
+  <si>
+    <t>(201) 409-6459</t>
+  </si>
+  <si>
+    <t>235 Main St, Paterson, NJ, 07505, Paterson, NJ 07522</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentistry+Paterson/data=!4m7!3m6!1s0x89c2fdce5b60acbf:0x17dcecc44bb64bc8!8m2!3d40.9164399!4d-74.1734544!16s%2Fg%2F11vwr9csz8!19sChIJv6xgW879wokRyEu2S8Ts3Bc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:34.523Z</t>
+  </si>
+  <si>
+    <t>Alvins Dental Laboratory</t>
+  </si>
+  <si>
+    <t>(973) 278-6858</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>86 Washington St #88, Paterson, NJ 07505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Alvins+Dental+Laboratory/data=!4m7!3m6!1s0x89c2fdcabeb008e9:0xbbff2710265b11a4!8m2!3d40.9186736!4d-74.172227!16s%2Fg%2F1tmk9fc9!19sChIJ6Qiwvsr9wokRpBFbJhAn_7s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:36.407Z</t>
+  </si>
+  <si>
+    <t>Emele Michael</t>
+  </si>
+  <si>
+    <t>(973) 247-1010</t>
+  </si>
+  <si>
+    <t>Medical clinic</t>
+  </si>
+  <si>
+    <t>635 Broadway, Paterson, NJ 07514</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emele+Michael/data=!4m7!3m6!1s0x89c2fc6a8b7934a9:0xfb31ff2bb2762abb!8m2!3d40.9184816!4d-74.146371!16s%2Fg%2F1tgff97t!19sChIJqTR5i2r8wokRuyp2siv_Mfs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:38.660Z</t>
+  </si>
+  <si>
+    <t>Dr. Ghassan S. Atalla, DDS</t>
+  </si>
+  <si>
+    <t>(973) 684-3803</t>
+  </si>
+  <si>
+    <t>1 W Broadway, Paterson, NJ 07505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ghassan+S.+Atalla,+DDS/data=!4m7!3m6!1s0x89c2fdca8c2bb86f:0x1ca30c4cc3709123!8m2!3d40.9191664!4d-74.1735158!16s%2Fg%2F1tqnmkv7!19sChIJb7grjMr9wokRI5Fww0wMoxw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:40.413Z</t>
+  </si>
+  <si>
+    <t>Implant Denture LLC</t>
+  </si>
+  <si>
+    <t>(973) 787-5743</t>
+  </si>
+  <si>
+    <t>Denture care center</t>
+  </si>
+  <si>
+    <t>689 E 31st St, Paterson, NJ 07513</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Implant+Denture+LLC/data=!4m7!3m6!1s0x89c2fdcb1bfea4b1:0x7dae7ace563b69fc!8m2!3d40.9022941!4d-74.146826!16s%2Fg%2F11jzc_dlxd!19sChIJsaT-G8v9wokR_Gk7Vs56rn0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:42.055Z</t>
+  </si>
+  <si>
+    <t>Dao Anh Cao</t>
+  </si>
+  <si>
+    <t>(973) 754-4250</t>
+  </si>
+  <si>
+    <t>11 Getty Ave, Paterson, NJ 07503</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dao+Anh+Cao/data=!4m7!3m6!1s0x89c2fdcea696bccd:0x6dc7b21a2a33a203!8m2!3d40.9151565!4d-74.1779731!16s%2Fg%2F1tfxhmj4!19sChIJzbyWps79wokRA6IzKhqyx20?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:44.541Z</t>
+  </si>
+  <si>
+    <t>Clifton Medical Care ll</t>
+  </si>
+  <si>
+    <t>(862) 249-4901</t>
+  </si>
+  <si>
+    <t>764 Main St Suite 302, Paterson, NJ 07503</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clifton+Medical+Care+ll/data=!4m7!3m6!1s0x89c2ffad02075ba7:0xa7f0c2176f43f50!8m2!3d40.9003977!4d-74.1653284!16s%2Fg%2F11bbrn98jn!19sChIJp1sHAq3_wokRUD_0diEMfwo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:33:47.361Z</t>
+  </si>
+  <si>
+    <t>Rojas Carlos a DDS</t>
+  </si>
+  <si>
+    <t>(973) 977-8181</t>
+  </si>
+  <si>
+    <t>630 11th Ave, Paterson, NJ 07514</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rojas+Carlos+a+DDS/data=!4m7!3m6!1s0x89c2fc6ea3a73a13:0x5092f2a08a42ba1d!8m2!3d40.9206181!4d-74.1401429!16s%2Fg%2F1thzvqtr!19sChIJEzqno278wokRHbpCiqDyklA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:34:01.051Z</t>
+  </si>
+  <si>
+    <t>Aesthetic Dental Care of New Jersey</t>
+  </si>
+  <si>
+    <t>(973) 227-8998</t>
+  </si>
+  <si>
+    <t>336 Union Blvd, Totowa, NJ 07512</t>
+  </si>
+  <si>
+    <t>Totowa</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aesthetic+Dental+Care+of+New+Jersey/data=!4m7!3m6!1s0x89c3010e8b4fd839:0x8cb57f001088d5d7!8m2!3d40.9039398!4d-74.2115797!16s%2Fg%2F1vm_ytx7!19sChIJOdhPiw4Bw4kR19WIEAB_tYw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:34:06.423Z</t>
+  </si>
+  <si>
+    <t>All Family Dentistry LLC</t>
+  </si>
+  <si>
+    <t>(973) 345-5550</t>
+  </si>
+  <si>
+    <t>669 Broadway #1, Paterson, NJ 07514</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/All+Family+Dentistry+LLC/data=!4m7!3m6!1s0x89c2fc6afbfcb10f:0x7a38d2e38363542a!8m2!3d40.9185224!4d-74.144801!16s%2Fg%2F1tfgf523!19sChIJD7H8-2r8wokRKlRjg-PSOHo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:34:15.760Z</t>
+  </si>
+  <si>
+    <t>Paterson Family Dental</t>
+  </si>
+  <si>
+    <t>(973) 225-9975</t>
+  </si>
+  <si>
+    <t>family dentistry</t>
+  </si>
+  <si>
+    <t>1010 Main St #6, Paterson, NJ 07503</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Paterson+Family+Dental/data=!4m7!3m6!1s0x89c2fe9b5ec1992b:0x6f33183202c4707b!8m2!3d40.8934628!4d-74.1590067!16s%2Fg%2F1th5dhk_!19sChIJK5nBXpv-wokRe3DEAjIYM28?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:34:20.582Z</t>
+  </si>
+  <si>
+    <t>Dr. Elana S. Wolf, DMD</t>
+  </si>
+  <si>
+    <t>(973) 742-4200</t>
+  </si>
+  <si>
+    <t>140 Market St 2nd floor, Paterson, NJ 07505</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Elana+S.+Wolf,+DMD/data=!4m7!3m6!1s0x89c2fdcb3dce43b5:0xd42209fc4a92ec8a!8m2!3d40.9163612!4d-74.1721857!16s%2Fg%2F1tcxw547!19sChIJtUPOPcv9wokRiuySSvwJItQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:35:31.676Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist of Hawthorne NJ</t>
+  </si>
+  <si>
+    <t>(973) 323-2235</t>
+  </si>
+  <si>
+    <t>625 Lafayette Ave #200, Hawthorne, NJ 07506</t>
+  </si>
+  <si>
+    <t>Hawthorne</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+of+Hawthorne+NJ/data=!4m7!3m6!1s0x89c2fd70d3a67bfd:0xc3e05581baed1c02!8m2!3d40.9597404!4d-74.1553655!16s%2Fg%2F11q959v_5z!19sChIJ_Xum03D9wokRAhztuoFV4MM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:35:57.496Z</t>
+  </si>
+  <si>
+    <t>Dr. Shrimattie A. Ramnauth, DMD</t>
+  </si>
+  <si>
+    <t>(973) 754-2000</t>
+  </si>
+  <si>
+    <t>Barber shop</t>
+  </si>
+  <si>
+    <t>703 Main St, Paterson, NJ 07503</t>
+  </si>
+  <si>
+    <t>Sunday11 AM–9 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Shrimattie+A.+Ramnauth,+DMD/data=!4m7!3m6!1s0x89c2fc2bca354d0f:0x8972e1b292bc8644!8m2!3d40.9022582!4d-74.1661378!16s%2Fg%2F1td395f1!19sChIJD001yiv8wokRRIa8krLhcok?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:35:59.228Z</t>
+  </si>
+  <si>
+    <t>Dr. Juan J. Alvarez, DMD</t>
+  </si>
+  <si>
+    <t>(973) 790-6594</t>
+  </si>
+  <si>
+    <t>32 Clinton St, Paterson, NJ 07522</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Juan+J.+Alvarez,+DMD/data=!4m7!3m6!1s0x89c2fdb4bc60d9eb:0xeb8438119da0c6a4!8m2!3d40.9245725!4d-74.1718417!16s%2Fg%2F1tm8lj99!19sChIJ69lgvLT9wokRpMagnRE4hOs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:36:13.005Z</t>
+  </si>
+  <si>
+    <t>Dr. Paul Y. Erdogan, DDS</t>
+  </si>
+  <si>
+    <t>(973) 523-8400</t>
+  </si>
+  <si>
+    <t>838 Main St, Paterson, NJ 07503</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Paul+Y.+Erdogan,+DDS/data=!4m7!3m6!1s0x89c2fe82756d4e3d:0xbc9b19251ad7cd98!8m2!3d40.8984087!4d-74.1632474!16s%2Fg%2F1tngr6x2!19sChIJPU5tdYL-wokRmM3XGiUZm7w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:36:14.681Z</t>
+  </si>
+  <si>
+    <t>Natural Cosmetics</t>
+  </si>
+  <si>
+    <t>(973) 818-6531</t>
+  </si>
+  <si>
+    <t>Permanent make-up clinic</t>
+  </si>
+  <si>
+    <t>256 Bergen Blvd Ste 206, Woodland Park, NJ 07424</t>
+  </si>
+  <si>
+    <t>Woodland Park</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Natural+Cosmetics/data=!4m7!3m6!1s0x8ced0ece383c26a7:0x9fb44a3e7784b54e!8m2!3d40.8945527!4d-74.2129244!16s%2Fg%2F11nnwknsrn!19sChIJpyY8OM4O7YwRTrWEdz5KtJ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:36:46.513Z</t>
+  </si>
+  <si>
+    <t>Alex Zusin, DMD</t>
+  </si>
+  <si>
+    <t>(973) 694-2000</t>
+  </si>
+  <si>
+    <t>Periodontist</t>
+  </si>
+  <si>
+    <t>1501 Hamburg Tpke #304, Wayne, NJ 07470</t>
+  </si>
+  <si>
+    <t>Wayne</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Alex+Zusin,+DMD/data=!4m7!3m6!1s0x89c303f00ad342fb:0xb2be793807f2907b!8m2!3d40.9641009!4d-74.2547277!16s%2Fg%2F11t7zrh533!19sChIJ-0LTCvADw4kRe5DyBzh5vrI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:11.715Z</t>
+  </si>
+  <si>
+    <t>Dr. Fadi Beydoun, DMD</t>
+  </si>
+  <si>
+    <t>(973) 777-6363</t>
+  </si>
+  <si>
+    <t>529 Clifton Ave, Clifton, NJ 07011</t>
+  </si>
+  <si>
+    <t>Clifton</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Fadi+Beydoun,+DMD/data=!4m7!3m6!1s0x89c3b4397cfd3de3:0x9f49418e3357be0e!8m2!3d40.8735407!4d-74.1484189!16s%2Fg%2F1ts3069d!19sChIJ4z39fDm0w4kRDr5XM45BSZ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:13.560Z</t>
+  </si>
+  <si>
+    <t>Dr. Thomas M. Scorziello, DMD</t>
+  </si>
+  <si>
+    <t>(973) 904-1400</t>
+  </si>
+  <si>
+    <t>601 Hamburg Tpke, Wayne, NJ 07470</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Thomas+M.+Scorziello,+DMD/data=!4m7!3m6!1s0x89c2fd7d58d8004d:0xc237ce600e88cc53!8m2!3d40.9547939!4d-74.2181145!16s%2Fg%2F1tflncg4!19sChIJTQDYWH39wokRU8yIDmDON8I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:15.881Z</t>
+  </si>
+  <si>
+    <t>Andrew H Sorger, DDS</t>
+  </si>
+  <si>
+    <t>(973) 742-1200</t>
+  </si>
+  <si>
+    <t>646 Broadway #2, Paterson, NJ 07514</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Andrew+H+Sorger,+DDS/data=!4m7!3m6!1s0x89c2fc6af2e0b8d7:0x39455fb485c1f3ec!8m2!3d40.9180947!4d-74.1459777!16s%2Fg%2F1vm7cd64!19sChIJ17jg8mr8wokR7PPBhbRfRTk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:17.548Z</t>
+  </si>
+  <si>
+    <t>unique Family Dentistry</t>
+  </si>
+  <si>
+    <t>(908) 965-1212</t>
+  </si>
+  <si>
+    <t>315 Elmora Ave Ste 104, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/unique+Family+Dentistry/data=!4m7!3m6!1s0x89c3b2a41704e90f:0x79b141e26c604610!8m2!3d40.6659537!4d-74.2337714!16s%2Fg%2F1tf9ts1b!19sChIJD-kEF6Syw4kREEZgbOJBsXk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:29.014Z</t>
+  </si>
+  <si>
+    <t>American Dental Group.</t>
+  </si>
+  <si>
+    <t>(908) 353-5400</t>
+  </si>
+  <si>
+    <t>14 Winfield Scott Plaza A, Elizabeth, NJ 07201</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/American+Dental+Group./data=!4m7!3m6!1s0x89c24d5160614fa3:0x7b75acc0a334b6b8!8m2!3d40.6624375!4d-74.211801!16s%2Fg%2F11c74h1vvx!19sChIJo09hYFFNwokRuLY0o8CsdXs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:30.633Z</t>
+  </si>
+  <si>
+    <t>Eli 1 Dental</t>
+  </si>
+  <si>
+    <t>(908) 352-2313</t>
+  </si>
+  <si>
+    <t>230 W Jersey St # L6, Elizabeth, NJ 07202</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Eli+1+Dental/data=!4m7!3m6!1s0x89c3b3c95a43d785:0xc9d948a9eb2bf57e!8m2!3d40.6629913!4d-74.224082!16s%2Fg%2F11ld3wt35r!19sChIJhddDWsmzw4kRfvUr66lI2ck?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:32.526Z</t>
+  </si>
+  <si>
+    <t>Associated Dental of Elizabeth</t>
+  </si>
+  <si>
+    <t>(908) 353-6655</t>
+  </si>
+  <si>
+    <t>444 Morris Ave, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Associated+Dental+of+Elizabeth/data=!4m7!3m6!1s0x89c3ad55bbc42b0f:0x65e4f00b152432f!8m2!3d40.6717364!4d-74.2218037!16s%2Fg%2F1tl1jv5y!19sChIJDyvEu1Wtw4kRL0NSsQBPXgY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:34.262Z</t>
+  </si>
+  <si>
+    <t>De Pinho Frank DDS Center</t>
+  </si>
+  <si>
+    <t>(908) 820-4772</t>
+  </si>
+  <si>
+    <t>520 Westfield Ave #209, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/De+Pinho+Frank+DDS+Center/data=!4m7!3m6!1s0x89c3b2a433887bad:0x34ea515c0a01ed25!8m2!3d40.6656576!4d-74.2327521!16s%2Fg%2F1x6q2pp1!19sChIJrXuIM6Syw4kRJe0BClxR6jQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:36.305Z</t>
+  </si>
+  <si>
+    <t>Dr. Aaron M Parada, DDS, LLC</t>
+  </si>
+  <si>
+    <t>(908) 354-0030</t>
+  </si>
+  <si>
+    <t>643 Elizabeth Ave, Elizabeth, NJ 07206</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Aaron+M+Parada,+DDS,+LLC/data=!4m7!3m6!1s0x89c24df899cd4f39:0x9fc85b3224b79e84!8m2!3d40.6573878!4d-74.2008619!16s%2Fg%2F11nx3540vn!19sChIJOU_NmfhNwokRhJ63JDJbyJ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:37.926Z</t>
+  </si>
+  <si>
+    <t>Marticorena Otilia DDS</t>
+  </si>
+  <si>
+    <t>(908) 520-8724</t>
+  </si>
+  <si>
+    <t>768 Newark Ave, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Marticorena+Otilia+DDS/data=!4m7!3m6!1s0x89c252b0fc468d47:0x479e905cd0363e8e!8m2!3d40.6811412!4d-74.2090856!16s%2Fg%2F1tywyvtr!19sChIJR41G_LBSwokRjj420FyQnkc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:39.780Z</t>
+  </si>
+  <si>
+    <t>Color Plaza Dental</t>
+  </si>
+  <si>
+    <t>(908) 436-0100</t>
+  </si>
+  <si>
+    <t>1000 S Elmora Ave #1E, Elizabeth, NJ 07202</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Color+Plaza+Dental/data=!4m7!3m6!1s0x89c3b2b6f35609ad:0xb954adfb6c0c1dae!8m2!3d40.6523873!4d-74.2250859!16s%2Fg%2F1tf29mhn!19sChIJrQlW87ayw4kRrh0MbPutVLk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:41.926Z</t>
+  </si>
+  <si>
+    <t>Supreme Dental Lab</t>
+  </si>
+  <si>
+    <t>(908) 558-1143</t>
+  </si>
+  <si>
+    <t>628 3rd Ave, Elizabeth, NJ 07202</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Supreme+Dental+Lab/data=!4m7!3m6!1s0x89c24d4579a4ba1b:0x80c4b425c4298efa!8m2!3d40.655557!4d-74.205598!16s%2Fg%2F1tjprdnf!19sChIJG7qkeUVNwokR-o4pxCW0xIA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:44.808Z</t>
+  </si>
+  <si>
+    <t>B &amp; K Family Dental</t>
+  </si>
+  <si>
+    <t>(908) 354-1500</t>
+  </si>
+  <si>
+    <t>707 Elizabeth Ave, Elizabeth, NJ 07201</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/B+%26+K+Family+Dental/data=!4m7!3m6!1s0x89c24d5b3f52f2db:0xcce7baec56a4bb3d!8m2!3d40.6582914!4d-74.2018315!16s%2Fg%2F1txfq1lx!19sChIJ2_JSP1tNwokRPbukVuy658w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:37:59.753Z</t>
+  </si>
+  <si>
+    <t>Carla Dersarkissian</t>
+  </si>
+  <si>
+    <t>(908) 282-6998</t>
+  </si>
+  <si>
+    <t>Endodontist</t>
+  </si>
+  <si>
+    <t>230 W Jersey St #302, Elizabeth, NJ 07202</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Carla+Dersarkissian/data=!4m7!3m6!1s0x89c3b2ae8662d981:0xefbb4a292d34cb3!8m2!3d40.6629946!4d-74.2241304!16s%2Fg%2F1tdry7ql!19sChIJgdlihq6yw4kRs0zTkqK0-w4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:01.570Z</t>
+  </si>
+  <si>
+    <t>Dr. Beatriz A. Fernandez, DMD</t>
+  </si>
+  <si>
+    <t>(908) 354-0800</t>
+  </si>
+  <si>
+    <t>230 W Jersey St #208, Elizabeth, NJ 07202</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Beatriz+A.+Fernandez,+DMD/data=!4m7!3m6!1s0x89c3b2ae8662d981:0x9961a34e12e2d796!8m2!3d40.6629913!4d-74.224082!16s%2Fg%2F1tfgqb99!19sChIJgdlihq6yw4kRltfiEk6jYZk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:03.644Z</t>
+  </si>
+  <si>
+    <t>Dr. Jacob Plawner</t>
+  </si>
+  <si>
+    <t>(908) 354-8678</t>
+  </si>
+  <si>
+    <t>700 N Broad St, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jacob+Plawner/data=!4m7!3m6!1s0x89c252b26ee113d9:0x61ccab7a711dd9e6!8m2!3d40.6796909!4d-74.2140655!16s%2Fg%2F11k3xt3nkk!19sChIJ2RPhbrJSwokR5tkdcXqrzGE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:05.819Z</t>
+  </si>
+  <si>
+    <t>Dr. Mira Peyyeti</t>
+  </si>
+  <si>
+    <t>(908) 352-5205</t>
+  </si>
+  <si>
+    <t>15 Prince St, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Mira+Peyyeti/data=!4m7!3m6!1s0x89c252aae4cb5d05:0x142c96850b838c96!8m2!3d40.6711613!4d-74.2157516!16s%2Fg%2F11qgb6kc4z!19sChIJBV3L5KpSwokRloyDC4WWLBQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:07.697Z</t>
+  </si>
+  <si>
+    <t>Dr. Claudia Rodríguez-Peña DDS</t>
+  </si>
+  <si>
+    <t>(908) 520-8733</t>
+  </si>
+  <si>
+    <t>324 Morris Ave, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Claudia+Rodr%C3%ADguez-Pe%C3%B1a+DDS/data=!4m7!3m6!1s0x89c3b2aaa853eb2b:0xcad83594a0657512!8m2!3d40.6693977!4d-74.2185713!16s%2Fg%2F11c3q4fr94!19sChIJK-tTqKqyw4kREnVloJQ12Mo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:09.285Z</t>
+  </si>
+  <si>
+    <t>Elmora Orthodontic &amp; Family Dental</t>
+  </si>
+  <si>
+    <t>(908) 527-1194</t>
+  </si>
+  <si>
+    <t>144 Elmora Ave #4, Elizabeth, NJ 07202</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Elmora+Orthodontic+%26+Family+Dental/data=!4m7!3m6!1s0x89c3b2a4cf18def7:0x4212ef2474f66fba!8m2!3d40.6622187!4d-74.2338103!16s%2Fg%2F1tks77n5!19sChIJ994Yz6Syw4kRum_2dCTvEkI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:11.302Z</t>
+  </si>
+  <si>
+    <t>Dr. Alina M. Betancourt, DMD</t>
+  </si>
+  <si>
+    <t>(908) 520-8726</t>
+  </si>
+  <si>
+    <t>570 N Broad St Ste 6, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Alina+M.+Betancourt,+DMD/data=!4m7!3m6!1s0x89c252ac373fd549:0x7ce36e2055a32d94!8m2!3d40.6754345!4d-74.2135329!16s%2Fg%2F1tf87_g7!19sChIJSdU_N6xSwokRlC2jVSBu43w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:13.138Z</t>
+  </si>
+  <si>
+    <t>Dr. Joseph Banker</t>
+  </si>
+  <si>
+    <t>(908) 354-1490</t>
+  </si>
+  <si>
+    <t>105 Elmora Ave, Elizabeth, NJ 07202</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Joseph+Banker/data=!4m7!3m6!1s0x89c3b2badfc6aaab:0xa82c62c5226b7564!8m2!3d40.6604431!4d-74.2324912!16s%2Fg%2F11qgb6fcch!19sChIJq6rG37qyw4kRZHVrIsViLKg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:14.995Z</t>
+  </si>
+  <si>
+    <t>Guy Elliot Robinson, DDS</t>
+  </si>
+  <si>
+    <t>(908) 352-4314</t>
+  </si>
+  <si>
+    <t>149 Jefferson Ave, Elizabeth, NJ 07201</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Guy+Elliot+Robinson,+DDS/data=!4m7!3m6!1s0x89c24d55d52e6843:0xe12ac184c77a9f54!8m2!3d40.6662356!4d-74.2118268!16s%2Fg%2F1vbnq9vy!19sChIJQ2gu1VVNwokRVJ96x4TBKuE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:17.096Z</t>
+  </si>
+  <si>
+    <t>Dr. Rony Elyahouzadeh, DDS</t>
+  </si>
+  <si>
+    <t>(908) 520-8739</t>
+  </si>
+  <si>
+    <t>444 Morris Ave #1, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Rony+Elyahouzadeh,+DDS/data=!4m7!3m6!1s0x89c3ad55bbc42b0f:0x38724d56c120ce97!8m2!3d40.6717367!4d-74.221737!16s%2Fg%2F1thvhwmy!19sChIJDyvEu1Wtw4kRl84gwVZNcjg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:18.845Z</t>
+  </si>
+  <si>
+    <t>Yoomi Heo</t>
+  </si>
+  <si>
+    <t>(908) 469-9100</t>
+  </si>
+  <si>
+    <t>65 Jefferson Ave, Elizabeth, NJ 072012474</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Yoomi+Heo/data=!4m7!3m6!1s0x89c24d5405164fef:0x881e3e53822b325!8m2!3d40.6643413!4d-74.2126732!16s%2Fg%2F11sh2c3rxr!19sChIJ708WBVRNwokRJbMiOOXjgQg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:38:41.207Z</t>
+  </si>
+  <si>
+    <t>Galaxy Dental Supply &amp; Services</t>
+  </si>
+  <si>
+    <t>(908) 352-9529</t>
+  </si>
+  <si>
+    <t>Medical supply store</t>
+  </si>
+  <si>
+    <t>528 Spring St, Elizabeth, NJ 07201</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Galaxy+Dental+Supply+%26+Services/data=!4m7!3m6!1s0x89c252a6bd1d4899:0xf888fb5eda7d1286!8m2!3d40.6714139!4d-74.2016051!16s%2Fg%2F1td5mm6w!19sChIJmUgdvaZSwokRhhJ92l77iPg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:40:12.893Z</t>
+  </si>
+  <si>
+    <t>Dr. Pardeep K. Sidhu, DDS</t>
+  </si>
+  <si>
+    <t>(908) 352-4438</t>
+  </si>
+  <si>
+    <t>465 North Ave, Elizabeth, NJ 07208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Pardeep+K.+Sidhu,+DDS/data=!4m7!3m6!1s0x89c3b2a7eb678633:0x13d330ff95509ac9!8m2!3d40.6707416!4d-74.2309407!16s%2Fg%2F1td4fhb2!19sChIJM4Zn66eyw4kRyZpQlf8w0xM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:40:14.735Z</t>
+  </si>
+  <si>
+    <t>Dr. Lysandra Plotkin</t>
+  </si>
+  <si>
+    <t>(908) 351-2106</t>
+  </si>
+  <si>
+    <t>1151 E Jersey St, Elizabeth, NJ 07201</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Lysandra+Plotkin/data=!4m7!3m6!1s0x89c24d543fe36e57:0xc62dd604d376e4c9!8m2!3d40.6651731!4d-74.2134766!16s%2Fg%2F11t86z5gpc!19sChIJV27jP1RNwokRyeR20wTWLcY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:40:17.914Z</t>
+  </si>
+  <si>
+    <t>Coleman Mark E DDS</t>
+  </si>
+  <si>
+    <t>(908) 436-2499</t>
+  </si>
+  <si>
+    <t>15 Elizabethtown Plaza, Elizabeth, NJ 07202</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Coleman+Mark+E+DDS/data=!4m7!3m6!1s0x89c24d532729ac51:0x5e171a3e1f8e16ef!8m2!3d40.6625987!4d-74.217086!16s%2Fg%2F1hc2rzslf!19sChIJUawpJ1NNwokR7xaOHz4aF14?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T03:40:23.063Z</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +2116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3173,6 +4019,2138 @@
         <v>292</v>
       </c>
     </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>293</v>
+      </c>
+      <c r="B47" t="s">
+        <v>294</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>295</v>
+      </c>
+      <c r="E47" t="s">
+        <v>289</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>88</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>165</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>296</v>
+      </c>
+      <c r="M47" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" t="s">
+        <v>299</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s">
+        <v>300</v>
+      </c>
+      <c r="E48" t="s">
+        <v>289</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>301</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>29</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>302</v>
+      </c>
+      <c r="M48" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>304</v>
+      </c>
+      <c r="B49" t="s">
+        <v>305</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>306</v>
+      </c>
+      <c r="E49" t="s">
+        <v>289</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>156</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>29</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>307</v>
+      </c>
+      <c r="M49" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>309</v>
+      </c>
+      <c r="B50" t="s">
+        <v>310</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>311</v>
+      </c>
+      <c r="E50" t="s">
+        <v>289</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>312</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>313</v>
+      </c>
+      <c r="M50" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>315</v>
+      </c>
+      <c r="B51" t="s">
+        <v>316</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>317</v>
+      </c>
+      <c r="E51" t="s">
+        <v>289</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>55</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>318</v>
+      </c>
+      <c r="M51" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>320</v>
+      </c>
+      <c r="B52" t="s">
+        <v>321</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>322</v>
+      </c>
+      <c r="E52" t="s">
+        <v>289</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>323</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>29</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>324</v>
+      </c>
+      <c r="M52" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>326</v>
+      </c>
+      <c r="B53" t="s">
+        <v>327</v>
+      </c>
+      <c r="C53" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" t="s">
+        <v>328</v>
+      </c>
+      <c r="E53" t="s">
+        <v>289</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>156</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>89</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>329</v>
+      </c>
+      <c r="M53" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>331</v>
+      </c>
+      <c r="B54" t="s">
+        <v>332</v>
+      </c>
+      <c r="C54" t="s">
+        <v>333</v>
+      </c>
+      <c r="D54" t="s">
+        <v>334</v>
+      </c>
+      <c r="E54" t="s">
+        <v>289</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>88</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>89</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>335</v>
+      </c>
+      <c r="M54" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>337</v>
+      </c>
+      <c r="B55" t="s">
+        <v>338</v>
+      </c>
+      <c r="C55" t="s">
+        <v>339</v>
+      </c>
+      <c r="D55" t="s">
+        <v>340</v>
+      </c>
+      <c r="E55" t="s">
+        <v>289</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>341</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>89</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>342</v>
+      </c>
+      <c r="M55" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>344</v>
+      </c>
+      <c r="B56" t="s">
+        <v>345</v>
+      </c>
+      <c r="C56" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" t="s">
+        <v>346</v>
+      </c>
+      <c r="E56" t="s">
+        <v>289</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>312</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>89</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>347</v>
+      </c>
+      <c r="M56" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>349</v>
+      </c>
+      <c r="B57" t="s">
+        <v>350</v>
+      </c>
+      <c r="C57" t="s">
+        <v>351</v>
+      </c>
+      <c r="D57" t="s">
+        <v>352</v>
+      </c>
+      <c r="E57" t="s">
+        <v>289</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>88</v>
+      </c>
+      <c r="I57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J57" t="s">
+        <v>89</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>354</v>
+      </c>
+      <c r="M57" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>356</v>
+      </c>
+      <c r="B58" t="s">
+        <v>357</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>358</v>
+      </c>
+      <c r="E58" t="s">
+        <v>289</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>341</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>29</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>359</v>
+      </c>
+      <c r="M58" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>361</v>
+      </c>
+      <c r="B59" t="s">
+        <v>362</v>
+      </c>
+      <c r="C59" t="s">
+        <v>339</v>
+      </c>
+      <c r="D59" t="s">
+        <v>363</v>
+      </c>
+      <c r="E59" t="s">
+        <v>289</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>164</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>29</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>364</v>
+      </c>
+      <c r="M59" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>366</v>
+      </c>
+      <c r="B60" t="s">
+        <v>367</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" t="s">
+        <v>368</v>
+      </c>
+      <c r="E60" t="s">
+        <v>289</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>88</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>89</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>369</v>
+      </c>
+      <c r="M60" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>371</v>
+      </c>
+      <c r="B61" t="s">
+        <v>372</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" t="s">
+        <v>373</v>
+      </c>
+      <c r="E61" t="s">
+        <v>374</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>62</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>29</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>375</v>
+      </c>
+      <c r="M61" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>377</v>
+      </c>
+      <c r="B62" t="s">
+        <v>378</v>
+      </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" t="s">
+        <v>379</v>
+      </c>
+      <c r="E62" t="s">
+        <v>289</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>251</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s">
+        <v>89</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>380</v>
+      </c>
+      <c r="M62" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>382</v>
+      </c>
+      <c r="B63" t="s">
+        <v>383</v>
+      </c>
+      <c r="C63" t="s">
+        <v>384</v>
+      </c>
+      <c r="D63" t="s">
+        <v>385</v>
+      </c>
+      <c r="E63" t="s">
+        <v>289</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>234</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>89</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>386</v>
+      </c>
+      <c r="M63" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>388</v>
+      </c>
+      <c r="B64" t="s">
+        <v>389</v>
+      </c>
+      <c r="C64" t="s">
+        <v>112</v>
+      </c>
+      <c r="D64" t="s">
+        <v>390</v>
+      </c>
+      <c r="E64" t="s">
+        <v>289</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>89</v>
+      </c>
+      <c r="I64" t="s">
+        <v>114</v>
+      </c>
+      <c r="J64" t="s">
+        <v>89</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>391</v>
+      </c>
+      <c r="M64" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>393</v>
+      </c>
+      <c r="B65" t="s">
+        <v>394</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" t="s">
+        <v>395</v>
+      </c>
+      <c r="E65" t="s">
+        <v>396</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>88</v>
+      </c>
+      <c r="I65" t="s">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s">
+        <v>29</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>397</v>
+      </c>
+      <c r="M65" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>399</v>
+      </c>
+      <c r="B66" t="s">
+        <v>400</v>
+      </c>
+      <c r="C66" t="s">
+        <v>401</v>
+      </c>
+      <c r="D66" t="s">
+        <v>402</v>
+      </c>
+      <c r="E66" t="s">
+        <v>289</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>89</v>
+      </c>
+      <c r="I66" t="s">
+        <v>114</v>
+      </c>
+      <c r="J66" t="s">
+        <v>403</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>404</v>
+      </c>
+      <c r="M66" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>406</v>
+      </c>
+      <c r="B67" t="s">
+        <v>407</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>408</v>
+      </c>
+      <c r="E67" t="s">
+        <v>289</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>89</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>409</v>
+      </c>
+      <c r="M67" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>411</v>
+      </c>
+      <c r="B68" t="s">
+        <v>412</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>413</v>
+      </c>
+      <c r="E68" t="s">
+        <v>289</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>88</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>89</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>414</v>
+      </c>
+      <c r="M68" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>416</v>
+      </c>
+      <c r="B69" t="s">
+        <v>417</v>
+      </c>
+      <c r="C69" t="s">
+        <v>418</v>
+      </c>
+      <c r="D69" t="s">
+        <v>419</v>
+      </c>
+      <c r="E69" t="s">
+        <v>420</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s">
+        <v>89</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>421</v>
+      </c>
+      <c r="M69" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>423</v>
+      </c>
+      <c r="B70" t="s">
+        <v>424</v>
+      </c>
+      <c r="C70" t="s">
+        <v>425</v>
+      </c>
+      <c r="D70" t="s">
+        <v>426</v>
+      </c>
+      <c r="E70" t="s">
+        <v>427</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>88</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>29</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>428</v>
+      </c>
+      <c r="M70" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>430</v>
+      </c>
+      <c r="B71" t="s">
+        <v>431</v>
+      </c>
+      <c r="C71" t="s">
+        <v>154</v>
+      </c>
+      <c r="D71" t="s">
+        <v>432</v>
+      </c>
+      <c r="E71" t="s">
+        <v>433</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>88</v>
+      </c>
+      <c r="I71" t="s">
+        <v>37</v>
+      </c>
+      <c r="J71" t="s">
+        <v>89</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>434</v>
+      </c>
+      <c r="M71" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>436</v>
+      </c>
+      <c r="B72" t="s">
+        <v>437</v>
+      </c>
+      <c r="C72" t="s">
+        <v>154</v>
+      </c>
+      <c r="D72" t="s">
+        <v>438</v>
+      </c>
+      <c r="E72" t="s">
+        <v>427</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>88</v>
+      </c>
+      <c r="I72" t="s">
+        <v>177</v>
+      </c>
+      <c r="J72" t="s">
+        <v>89</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>439</v>
+      </c>
+      <c r="M72" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>441</v>
+      </c>
+      <c r="B73" t="s">
+        <v>442</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>443</v>
+      </c>
+      <c r="E73" t="s">
+        <v>289</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>88</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
+        <v>89</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>444</v>
+      </c>
+      <c r="M73" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>446</v>
+      </c>
+      <c r="B74" t="s">
+        <v>447</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" t="s">
+        <v>448</v>
+      </c>
+      <c r="E74" t="s">
+        <v>95</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>73</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>29</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>449</v>
+      </c>
+      <c r="M74" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>451</v>
+      </c>
+      <c r="B75" t="s">
+        <v>452</v>
+      </c>
+      <c r="C75" t="s">
+        <v>339</v>
+      </c>
+      <c r="D75" t="s">
+        <v>453</v>
+      </c>
+      <c r="E75" t="s">
+        <v>95</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>156</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>29</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>454</v>
+      </c>
+      <c r="M75" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>456</v>
+      </c>
+      <c r="B76" t="s">
+        <v>457</v>
+      </c>
+      <c r="C76" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" t="s">
+        <v>458</v>
+      </c>
+      <c r="E76" t="s">
+        <v>95</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>88</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>29</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>459</v>
+      </c>
+      <c r="M76" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>461</v>
+      </c>
+      <c r="B77" t="s">
+        <v>462</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" t="s">
+        <v>463</v>
+      </c>
+      <c r="E77" t="s">
+        <v>95</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>278</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>29</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>464</v>
+      </c>
+      <c r="M77" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>466</v>
+      </c>
+      <c r="B78" t="s">
+        <v>467</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s">
+        <v>468</v>
+      </c>
+      <c r="E78" t="s">
+        <v>95</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>164</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>29</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>469</v>
+      </c>
+      <c r="M78" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>471</v>
+      </c>
+      <c r="B79" t="s">
+        <v>472</v>
+      </c>
+      <c r="C79" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" t="s">
+        <v>473</v>
+      </c>
+      <c r="E79" t="s">
+        <v>95</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>164</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
+        <v>29</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>474</v>
+      </c>
+      <c r="M79" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>476</v>
+      </c>
+      <c r="B80" t="s">
+        <v>477</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>478</v>
+      </c>
+      <c r="E80" t="s">
+        <v>95</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>55</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>29</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>479</v>
+      </c>
+      <c r="M80" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>481</v>
+      </c>
+      <c r="B81" t="s">
+        <v>482</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" t="s">
+        <v>483</v>
+      </c>
+      <c r="E81" t="s">
+        <v>95</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>484</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>29</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>485</v>
+      </c>
+      <c r="M81" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>487</v>
+      </c>
+      <c r="B82" t="s">
+        <v>488</v>
+      </c>
+      <c r="C82" t="s">
+        <v>333</v>
+      </c>
+      <c r="D82" t="s">
+        <v>489</v>
+      </c>
+      <c r="E82" t="s">
+        <v>95</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>89</v>
+      </c>
+      <c r="I82" t="s">
+        <v>114</v>
+      </c>
+      <c r="J82" t="s">
+        <v>89</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>490</v>
+      </c>
+      <c r="M82" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>492</v>
+      </c>
+      <c r="B83" t="s">
+        <v>493</v>
+      </c>
+      <c r="C83" t="s">
+        <v>85</v>
+      </c>
+      <c r="D83" t="s">
+        <v>494</v>
+      </c>
+      <c r="E83" t="s">
+        <v>95</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>234</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s">
+        <v>29</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>495</v>
+      </c>
+      <c r="M83" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>497</v>
+      </c>
+      <c r="B84" t="s">
+        <v>498</v>
+      </c>
+      <c r="C84" t="s">
+        <v>499</v>
+      </c>
+      <c r="D84" t="s">
+        <v>500</v>
+      </c>
+      <c r="E84" t="s">
+        <v>95</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>257</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s">
+        <v>89</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>501</v>
+      </c>
+      <c r="M84" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>503</v>
+      </c>
+      <c r="B85" t="s">
+        <v>504</v>
+      </c>
+      <c r="C85" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" t="s">
+        <v>505</v>
+      </c>
+      <c r="E85" t="s">
+        <v>95</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>88</v>
+      </c>
+      <c r="I85" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s">
+        <v>89</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>506</v>
+      </c>
+      <c r="M85" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>508</v>
+      </c>
+      <c r="B86" t="s">
+        <v>509</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" t="s">
+        <v>510</v>
+      </c>
+      <c r="E86" t="s">
+        <v>95</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>312</v>
+      </c>
+      <c r="I86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s">
+        <v>89</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>511</v>
+      </c>
+      <c r="M86" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>513</v>
+      </c>
+      <c r="B87" t="s">
+        <v>514</v>
+      </c>
+      <c r="C87" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" t="s">
+        <v>515</v>
+      </c>
+      <c r="E87" t="s">
+        <v>95</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
+        <v>88</v>
+      </c>
+      <c r="I87" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s">
+        <v>89</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" t="s">
+        <v>516</v>
+      </c>
+      <c r="M87" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>518</v>
+      </c>
+      <c r="B88" t="s">
+        <v>519</v>
+      </c>
+      <c r="C88" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" t="s">
+        <v>520</v>
+      </c>
+      <c r="E88" t="s">
+        <v>95</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>88</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s">
+        <v>89</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" t="s">
+        <v>521</v>
+      </c>
+      <c r="M88" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>523</v>
+      </c>
+      <c r="B89" t="s">
+        <v>524</v>
+      </c>
+      <c r="C89" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" t="s">
+        <v>525</v>
+      </c>
+      <c r="E89" t="s">
+        <v>95</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" t="s">
+        <v>176</v>
+      </c>
+      <c r="I89" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s">
+        <v>89</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>526</v>
+      </c>
+      <c r="M89" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>528</v>
+      </c>
+      <c r="B90" t="s">
+        <v>529</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>530</v>
+      </c>
+      <c r="E90" t="s">
+        <v>95</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>531</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>29</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>532</v>
+      </c>
+      <c r="M90" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>534</v>
+      </c>
+      <c r="B91" t="s">
+        <v>535</v>
+      </c>
+      <c r="C91" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" t="s">
+        <v>536</v>
+      </c>
+      <c r="E91" t="s">
+        <v>95</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" t="s">
+        <v>88</v>
+      </c>
+      <c r="I91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s">
+        <v>89</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" t="s">
+        <v>537</v>
+      </c>
+      <c r="M91" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>539</v>
+      </c>
+      <c r="B92" t="s">
+        <v>540</v>
+      </c>
+      <c r="C92" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" t="s">
+        <v>541</v>
+      </c>
+      <c r="E92" t="s">
+        <v>95</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" t="s">
+        <v>36</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s">
+        <v>89</v>
+      </c>
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" t="s">
+        <v>542</v>
+      </c>
+      <c r="M92" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>544</v>
+      </c>
+      <c r="B93" t="s">
+        <v>545</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" t="s">
+        <v>546</v>
+      </c>
+      <c r="E93" t="s">
+        <v>95</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>88</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>89</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" t="s">
+        <v>547</v>
+      </c>
+      <c r="M93" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>549</v>
+      </c>
+      <c r="B94" t="s">
+        <v>550</v>
+      </c>
+      <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
+        <v>551</v>
+      </c>
+      <c r="E94" t="s">
+        <v>95</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" t="s">
+        <v>312</v>
+      </c>
+      <c r="I94" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s">
+        <v>89</v>
+      </c>
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" t="s">
+        <v>552</v>
+      </c>
+      <c r="M94" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>554</v>
+      </c>
+      <c r="B95" t="s">
+        <v>555</v>
+      </c>
+      <c r="C95" t="s">
+        <v>556</v>
+      </c>
+      <c r="D95" t="s">
+        <v>557</v>
+      </c>
+      <c r="E95" t="s">
+        <v>95</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" t="s">
+        <v>88</v>
+      </c>
+      <c r="I95" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s">
+        <v>29</v>
+      </c>
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" t="s">
+        <v>558</v>
+      </c>
+      <c r="M95" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>560</v>
+      </c>
+      <c r="B96" t="s">
+        <v>561</v>
+      </c>
+      <c r="C96" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" t="s">
+        <v>562</v>
+      </c>
+      <c r="E96" t="s">
+        <v>95</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>88</v>
+      </c>
+      <c r="I96" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s">
+        <v>89</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" t="s">
+        <v>563</v>
+      </c>
+      <c r="M96" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>565</v>
+      </c>
+      <c r="B97" t="s">
+        <v>566</v>
+      </c>
+      <c r="C97" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" t="s">
+        <v>567</v>
+      </c>
+      <c r="E97" t="s">
+        <v>95</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>88</v>
+      </c>
+      <c r="I97" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s">
+        <v>89</v>
+      </c>
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" t="s">
+        <v>568</v>
+      </c>
+      <c r="M97" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>570</v>
+      </c>
+      <c r="B98" t="s">
+        <v>571</v>
+      </c>
+      <c r="C98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" t="s">
+        <v>572</v>
+      </c>
+      <c r="E98" t="s">
+        <v>95</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" t="s">
+        <v>89</v>
+      </c>
+      <c r="I98" t="s">
+        <v>114</v>
+      </c>
+      <c r="J98" t="s">
+        <v>89</v>
+      </c>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" t="s">
+        <v>573</v>
+      </c>
+      <c r="M98" t="s">
+        <v>574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
